--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,6 +804,153 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122390502</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8425</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-3, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>528354</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6454642</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>122308662</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -951,6 +951,278 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122427546</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98185</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-3, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>528354</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6454642</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122372198</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91472</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-1, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528360</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6454489</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -953,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427546</v>
+        <v>122372198</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>91472</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,46 +965,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528354</v>
+        <v>528360</v>
       </c>
       <c r="R4" t="n">
-        <v>6454642</v>
+        <v>6454489</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1031,27 +1026,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Min. 23 ex</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1061,17 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122372198</v>
+        <v>122427546</v>
       </c>
       <c r="B5" t="n">
-        <v>91472</v>
+        <v>98185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,41 +1101,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528360</v>
+        <v>528354</v>
       </c>
       <c r="R5" t="n">
-        <v>6454489</v>
+        <v>6454642</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1162,22 +1167,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,17 +1207,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1223,6 +1223,137 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122453538</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98185</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-8, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>528336</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6454669</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker:  58°13′58″N, 15°28′58″E</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308662</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>122390502</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>8430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>122372198</v>
       </c>
       <c r="B4" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>122427546</v>
       </c>
       <c r="B5" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122453538</v>
+        <v>122452446</v>
       </c>
       <c r="B6" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1318,7 +1318,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Min. 4 ex, sannolikt fler. Vill ej separera mossan pga fruset, med risk för att skada ex.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1338,7 +1343,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker:  58°13′58″N, 15°28′58″E</t>
+          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker: 58°13′57.5″N, 15°28′57.6″E</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308662</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>122372198</v>
       </c>
       <c r="B4" t="n">
-        <v>91484</v>
+        <v>91489</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>122427546</v>
       </c>
       <c r="B5" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122452446</v>
+        <v>122453538</v>
       </c>
       <c r="B6" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1318,12 +1318,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Min. 4 ex, sannolikt fler. Vill ej separera mossan pga fruset, med risk för att skada ex.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1343,7 +1338,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker: 58°13′57.5″N, 15°28′57.6″E</t>
+          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker:  58°13′58″N, 15°28′58″E</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308662</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -824,11 +819,6 @@
       <c r="E3" t="n">
         <v>106554</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Scolytus ratzeburgii</t>
@@ -923,11 +913,6 @@
           <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
           <t>Betula</t>
@@ -953,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122372198</v>
+        <v>122427546</v>
       </c>
       <c r="B4" t="n">
-        <v>91489</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,41 +950,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528360</v>
+        <v>528354</v>
       </c>
       <c r="R4" t="n">
-        <v>6454489</v>
+        <v>6454642</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1026,22 +1011,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,17 +1051,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427546</v>
+        <v>122372198</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>91494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,46 +1081,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>3298</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528354</v>
+        <v>528360</v>
       </c>
       <c r="R5" t="n">
-        <v>6454642</v>
+        <v>6454489</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1167,27 +1137,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Min. 23 ex</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,7 +1172,17 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1228,7 +1203,7 @@
         <v>122453538</v>
       </c>
       <c r="B6" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1242,11 +1217,6 @@
       </c>
       <c r="E6" t="n">
         <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308662</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -819,6 +824,11 @@
       <c r="E3" t="n">
         <v>106554</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Scolytus ratzeburgii</t>
@@ -913,6 +923,11 @@
           <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.</t>
         </is>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
       <c r="AK3" t="inlineStr">
         <is>
           <t>Betula</t>
@@ -938,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427546</v>
+        <v>122372198</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>91507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,41 +965,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3298</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528354</v>
+        <v>528360</v>
       </c>
       <c r="R4" t="n">
-        <v>6454642</v>
+        <v>6454489</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1011,27 +1026,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Min. 23 ex</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1061,17 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1069,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122372198</v>
+        <v>122427546</v>
       </c>
       <c r="B5" t="n">
-        <v>91494</v>
+        <v>98224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,36 +1101,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528360</v>
+        <v>528354</v>
       </c>
       <c r="R5" t="n">
-        <v>6454489</v>
+        <v>6454642</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1137,22 +1167,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,17 +1207,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,7 +1228,7 @@
         <v>122453538</v>
       </c>
       <c r="B6" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,6 +1242,11 @@
       </c>
       <c r="E6" t="n">
         <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308662</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>122372198</v>
       </c>
       <c r="B4" t="n">
-        <v>91507</v>
+        <v>91520</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>122427546</v>
       </c>
       <c r="B5" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>122453538</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -953,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122372198</v>
+        <v>122427546</v>
       </c>
       <c r="B4" t="n">
-        <v>91520</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,41 +965,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528360</v>
+        <v>528354</v>
       </c>
       <c r="R4" t="n">
-        <v>6454489</v>
+        <v>6454642</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1026,22 +1031,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,17 +1071,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427546</v>
+        <v>122372198</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>91520</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,46 +1101,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528354</v>
+        <v>528360</v>
       </c>
       <c r="R5" t="n">
-        <v>6454642</v>
+        <v>6454489</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1167,27 +1162,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Min. 23 ex</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,7 +1197,17 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308662</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427546</v>
+        <v>122372198</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>91521</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,46 +965,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528354</v>
+        <v>528360</v>
       </c>
       <c r="R4" t="n">
-        <v>6454642</v>
+        <v>6454489</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1031,27 +1026,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Min. 23 ex</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1061,17 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122372198</v>
+        <v>122427546</v>
       </c>
       <c r="B5" t="n">
-        <v>91520</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,41 +1101,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528360</v>
+        <v>528354</v>
       </c>
       <c r="R5" t="n">
-        <v>6454489</v>
+        <v>6454642</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1162,22 +1167,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,17 +1207,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122453538</v>
+        <v>122452446</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1318,7 +1318,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Min. 4 ex, sannolikt fler. Vill ej separera mossan pga fruset, med risk för att skada ex.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1338,7 +1343,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker:  58°13′58″N, 15°28′58″E</t>
+          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker: 58°13′57.5″N, 15°28′57.6″E</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -953,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122372198</v>
+        <v>122427546</v>
       </c>
       <c r="B4" t="n">
-        <v>91521</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,41 +965,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528360</v>
+        <v>528354</v>
       </c>
       <c r="R4" t="n">
-        <v>6454489</v>
+        <v>6454642</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1026,22 +1031,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,17 +1071,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427546</v>
+        <v>122372198</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>91521</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,46 +1101,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528354</v>
+        <v>528360</v>
       </c>
       <c r="R5" t="n">
-        <v>6454642</v>
+        <v>6454489</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1167,27 +1162,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Min. 23 ex</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,7 +1197,17 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122452446</v>
+        <v>122453538</v>
       </c>
       <c r="B6" t="n">
         <v>98240</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1318,12 +1318,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Min. 4 ex, sannolikt fler. Vill ej separera mossan pga fruset, med risk för att skada ex.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1343,7 +1338,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker: 58°13′57.5″N, 15°28′57.6″E</t>
+          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker:  58°13′58″N, 15°28′58″E</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308662</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427546</v>
+        <v>122372198</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>91522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,46 +965,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528354</v>
+        <v>528360</v>
       </c>
       <c r="R4" t="n">
-        <v>6454642</v>
+        <v>6454489</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1031,27 +1026,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Min. 23 ex</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1061,17 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122372198</v>
+        <v>122427546</v>
       </c>
       <c r="B5" t="n">
-        <v>91521</v>
+        <v>98241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,41 +1101,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528360</v>
+        <v>528354</v>
       </c>
       <c r="R5" t="n">
-        <v>6454489</v>
+        <v>6454642</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1162,22 +1167,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,17 +1207,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122453538</v>
+        <v>122452446</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1318,7 +1318,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Min. 4 ex, sannolikt fler. Vill ej separera mossan pga fruset, med risk för att skada ex.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1338,7 +1343,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker:  58°13′58″N, 15°28′58″E</t>
+          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker: 58°13′57.5″N, 15°28′57.6″E</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308662</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122372198</v>
+        <v>122427546</v>
       </c>
       <c r="B4" t="n">
-        <v>91522</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,41 +965,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528360</v>
+        <v>528354</v>
       </c>
       <c r="R4" t="n">
-        <v>6454489</v>
+        <v>6454642</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1026,22 +1031,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,17 +1071,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427546</v>
+        <v>122372198</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>91525</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,46 +1101,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528354</v>
+        <v>528360</v>
       </c>
       <c r="R5" t="n">
-        <v>6454642</v>
+        <v>6454489</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1167,27 +1162,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Min. 23 ex</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,7 +1197,17 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
         <v>122452446</v>
       </c>
       <c r="B6" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -953,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427546</v>
+        <v>122372198</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>91525</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,46 +965,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528354</v>
+        <v>528360</v>
       </c>
       <c r="R4" t="n">
-        <v>6454642</v>
+        <v>6454489</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1031,27 +1026,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Min. 23 ex</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1061,17 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122372198</v>
+        <v>122427546</v>
       </c>
       <c r="B5" t="n">
-        <v>91525</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,41 +1101,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528360</v>
+        <v>528354</v>
       </c>
       <c r="R5" t="n">
-        <v>6454489</v>
+        <v>6454642</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1162,22 +1167,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,17 +1207,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,6 +1359,148 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121642589</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8355</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-9, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>528205</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6454473</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrdominerat med inslag av t ex rönn, ek, hassel, björk. Gläntor. Lågor, stubbar, död ved förekommer. Koordinater fynd Geo tracker: 58°13′50.7″N, 15°28′48.8″E</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Not: Större del av trädstam ej markkontakt för själva fynd.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1501,6 +1501,158 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122797932</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8430</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-8, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>528336</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6454669</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°13′55.7″N, 15°28′58.2″E</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Delvis markkontakt.  # Betula</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>122372198</v>
       </c>
       <c r="B4" t="n">
-        <v>91525</v>
+        <v>91628</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>122427546</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122452446</v>
+        <v>122453538</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1318,12 +1318,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Min. 4 ex, sannolikt fler. Vill ej separera mossan pga fruset, med risk för att skada ex.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1343,7 +1338,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker: 58°13′57.5″N, 15°28′57.6″E</t>
+          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker:  58°13′58″N, 15°28′58″E</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -1228,7 +1228,7 @@
         <v>122453538</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -953,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122372198</v>
+        <v>122428481</v>
       </c>
       <c r="B4" t="n">
-        <v>91628</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,41 +965,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-8, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528360</v>
+        <v>528336</v>
       </c>
       <c r="R4" t="n">
-        <v>6454489</v>
+        <v>6454669</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1026,22 +1031,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>23 exemplar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,17 +1071,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 57.6 N, 15o28 59.2 E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427546</v>
+        <v>122372198</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>91628</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,46 +1101,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528354</v>
+        <v>528360</v>
       </c>
       <c r="R5" t="n">
-        <v>6454642</v>
+        <v>6454489</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1167,27 +1162,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Min. 23 ex</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,7 +1197,17 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av t ex ek, asp, björk. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer. Delvis fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122453538</v>
+        <v>122427546</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1269,14 +1269,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-8, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528336</v>
+        <v>528354</v>
       </c>
       <c r="R6" t="n">
-        <v>6454669</v>
+        <v>6454642</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1303,22 +1303,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Min. 23 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1338,7 +1343,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Död ved, stubbar, lågor i olika nedbrytningsstadier förekommer.  OBS: Koordinater på fyndplats, Geo tracker:  58°13′58″N, 15°28′58″E</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -988,7 +988,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>23 exemplar</t>
+          <t>49 räknade exemplar 9 ex tall vänster 6  ex tall höger 34 ex sluttning, ca 4 m bakom fynd tall vänster</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 57.6 N, 15o28 59.2 E</t>
+          <t>Barrdominerat med lövinslag. Koordinater fynd Geo tracker:  58°13′57.2″N, 15°28′59.5″E 9 ex tall vänster 6  ex tall höger 34 ex sluttning, ca 4 m bakom fynd tall vänster</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>122428481</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,6 +1653,116 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123035172</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90972</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vallsnäs, Haraldsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>528208</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6454471</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Toss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Toss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,6 +1763,707 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123380092</v>
+      </c>
+      <c r="B10" t="n">
+        <v>94854</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skvallerhagen, Skvallerhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>528379</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6454562</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog i branter</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123383363</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skvallerhagen, Skvallerhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>528362</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6454498</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 ex räknade.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123383615</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skvallerhagen, Skvallerhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>528366</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6454480</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>136 ex räknade, sannolikt fler.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123382746</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skvallerhagen, Skvallerhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>528338</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6454502</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>12 ex räknade.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123382241</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skvallerhagen, Skvallerhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>528337</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6454487</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>122428481</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>123035172</v>
       </c>
       <c r="B9" t="n">
-        <v>90972</v>
+        <v>90975</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123380092</v>
+        <v>123383363</v>
       </c>
       <c r="B10" t="n">
-        <v>94854</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1777,29 +1777,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1809,13 +1817,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528379</v>
+        <v>528362</v>
       </c>
       <c r="R10" t="n">
-        <v>6454562</v>
+        <v>6454498</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1844,7 +1852,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1854,7 +1862,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>10 ex räknade.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1869,22 +1882,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1902,10 +1905,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123383363</v>
+        <v>123382241</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1937,7 +1940,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1954,10 +1957,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528362</v>
+        <v>528337</v>
       </c>
       <c r="R11" t="n">
-        <v>6454498</v>
+        <v>6454487</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1989,7 +1992,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1999,12 +2002,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>10 ex räknade.</t>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2019,12 +2022,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2042,10 +2045,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123383615</v>
+        <v>123380092</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>94857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2054,42 +2057,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2098,10 +2089,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528366</v>
+        <v>528379</v>
       </c>
       <c r="R12" t="n">
-        <v>6454480</v>
+        <v>6454562</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2133,7 +2124,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2143,12 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2163,12 +2149,22 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2189,7 +2185,7 @@
         <v>123382746</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2326,10 +2322,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123382241</v>
+        <v>123383615</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2361,7 +2357,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2369,7 +2365,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2378,13 +2378,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528337</v>
+        <v>528366</v>
       </c>
       <c r="R14" t="n">
-        <v>6454487</v>
+        <v>6454480</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>122428481</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>123035172</v>
       </c>
       <c r="B9" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123383363</v>
+        <v>123383615</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1808,7 +1808,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1817,13 +1821,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528362</v>
+        <v>528366</v>
       </c>
       <c r="R10" t="n">
-        <v>6454498</v>
+        <v>6454480</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1852,7 +1856,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1862,12 +1866,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>10 ex räknade.</t>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1882,12 +1886,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1908,7 +1912,7 @@
         <v>123382241</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2045,10 +2049,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123380092</v>
+        <v>123383363</v>
       </c>
       <c r="B12" t="n">
-        <v>94857</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2057,29 +2061,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -2089,13 +2101,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528379</v>
+        <v>528362</v>
       </c>
       <c r="R12" t="n">
-        <v>6454562</v>
+        <v>6454498</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2124,7 +2136,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2134,7 +2146,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>10 ex räknade.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2149,22 +2166,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2185,7 +2192,7 @@
         <v>123382746</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2322,10 +2329,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123383615</v>
+        <v>123380092</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>94859</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2334,42 +2341,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2378,10 +2373,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528366</v>
+        <v>528379</v>
       </c>
       <c r="R14" t="n">
-        <v>6454480</v>
+        <v>6454562</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2423,12 +2418,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2443,12 +2433,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>122428481</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>123035172</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123383615</v>
+        <v>123382746</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1808,11 +1808,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1821,13 +1817,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528366</v>
+        <v>528338</v>
       </c>
       <c r="R10" t="n">
-        <v>6454480</v>
+        <v>6454502</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1866,12 +1862,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1886,12 +1882,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1909,10 +1905,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123382241</v>
+        <v>123380092</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>94865</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1921,37 +1917,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1961,13 +1949,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528337</v>
+        <v>528379</v>
       </c>
       <c r="R11" t="n">
-        <v>6454487</v>
+        <v>6454562</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1996,7 +1984,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2006,12 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2026,12 +2009,22 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2049,10 +2042,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123383363</v>
+        <v>123383615</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2084,7 +2077,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2092,7 +2085,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2101,13 +2098,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528362</v>
+        <v>528366</v>
       </c>
       <c r="R12" t="n">
-        <v>6454498</v>
+        <v>6454480</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2136,7 +2133,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2146,12 +2143,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>10 ex räknade.</t>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,12 +2163,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2189,10 +2186,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123382746</v>
+        <v>123383363</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2224,7 +2221,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2241,13 +2238,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528338</v>
+        <v>528362</v>
       </c>
       <c r="R13" t="n">
-        <v>6454502</v>
+        <v>6454498</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2276,7 +2273,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2286,12 +2283,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>12 ex räknade.</t>
+          <t>10 ex räknade.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2311,7 +2308,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2329,10 +2326,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123380092</v>
+        <v>123382241</v>
       </c>
       <c r="B14" t="n">
-        <v>94859</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2341,29 +2338,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2373,13 +2378,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528379</v>
+        <v>528337</v>
       </c>
       <c r="R14" t="n">
-        <v>6454562</v>
+        <v>6454487</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2418,7 +2423,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2433,22 +2443,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>122428481</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>123035172</v>
       </c>
       <c r="B9" t="n">
-        <v>90983</v>
+        <v>90986</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123382746</v>
+        <v>123380092</v>
       </c>
       <c r="B10" t="n">
-        <v>98376</v>
+        <v>94868</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1777,37 +1777,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1817,13 +1809,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528338</v>
+        <v>528379</v>
       </c>
       <c r="R10" t="n">
-        <v>6454502</v>
+        <v>6454562</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1852,7 +1844,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1862,12 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>12 ex räknade.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1882,12 +1869,22 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1905,10 +1902,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123380092</v>
+        <v>123382746</v>
       </c>
       <c r="B11" t="n">
-        <v>94865</v>
+        <v>98379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1917,29 +1914,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1949,13 +1954,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528379</v>
+        <v>528338</v>
       </c>
       <c r="R11" t="n">
-        <v>6454562</v>
+        <v>6454502</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1984,7 +1989,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1994,7 +1999,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2009,22 +2019,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
         <v>123383615</v>
       </c>
       <c r="B12" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123383363</v>
+        <v>123382241</v>
       </c>
       <c r="B13" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528362</v>
+        <v>528337</v>
       </c>
       <c r="R13" t="n">
-        <v>6454498</v>
+        <v>6454487</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>10 ex räknade.</t>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123382241</v>
+        <v>123383363</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528337</v>
+        <v>528362</v>
       </c>
       <c r="R14" t="n">
-        <v>6454487</v>
+        <v>6454498</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+          <t>10 ex räknade.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2464,6 +2464,315 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123693724</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90986</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-3, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>528354</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6454642</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrdominerat med lövinslag,  diameterspridning, död ved i olika nedbrytningsstadier  Koordinater fynd Geo tracker: 58°13′55.5″N, 15°29′00.3″E</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123690103</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-8, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>528336</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6454669</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Barrdominerat med lövinslag,  diameterspridning</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>122428481</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>123035172</v>
       </c>
       <c r="B9" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123380092</v>
+        <v>123383363</v>
       </c>
       <c r="B10" t="n">
-        <v>94868</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1777,29 +1777,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1809,13 +1817,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528379</v>
+        <v>528362</v>
       </c>
       <c r="R10" t="n">
-        <v>6454562</v>
+        <v>6454498</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1844,7 +1852,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1854,7 +1862,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>10 ex räknade.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1869,22 +1882,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1902,10 +1905,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123382746</v>
+        <v>123383615</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1937,7 +1940,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1945,7 +1948,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1954,13 +1961,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528338</v>
+        <v>528366</v>
       </c>
       <c r="R11" t="n">
-        <v>6454502</v>
+        <v>6454480</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1989,7 +1996,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1999,12 +2006,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>12 ex räknade.</t>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2019,12 +2026,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2042,10 +2049,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123383615</v>
+        <v>123382746</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2077,7 +2084,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2085,11 +2092,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2098,13 +2101,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528366</v>
+        <v>528338</v>
       </c>
       <c r="R12" t="n">
-        <v>6454480</v>
+        <v>6454502</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2133,7 +2136,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2143,12 +2146,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2163,12 +2166,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2189,7 +2192,7 @@
         <v>123382241</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2326,10 +2329,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123383363</v>
+        <v>123380092</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>94885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2338,37 +2341,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2378,13 +2373,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528362</v>
+        <v>528379</v>
       </c>
       <c r="R14" t="n">
-        <v>6454498</v>
+        <v>6454562</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2423,12 +2418,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 ex räknade.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2443,12 +2433,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123693724</v>
+        <v>123690103</v>
       </c>
       <c r="B15" t="n">
-        <v>90986</v>
+        <v>57503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2482,45 +2482,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-8, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528354</v>
+        <v>528336</v>
       </c>
       <c r="R15" t="n">
-        <v>6454642</v>
+        <v>6454669</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2552,7 +2549,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2562,7 +2559,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2571,7 +2568,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2582,32 +2578,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerat med lövinslag,  diameterspridning, död ved i olika nedbrytningsstadier  Koordinater fynd Geo tracker: 58°13′55.5″N, 15°29′00.3″E</t>
+          <t>Barrdominerat med lövinslag,  diameterspridning</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Grov ved</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Standing dead tree/snags # Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2625,10 +2616,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123690103</v>
+        <v>123693724</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>91003</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2641,42 +2632,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-8, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528336</v>
+        <v>528354</v>
       </c>
       <c r="R16" t="n">
-        <v>6454669</v>
+        <v>6454642</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2708,7 +2702,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2718,7 +2712,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2727,6 +2721,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2737,27 +2732,32 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrdominerat med lövinslag,  diameterspridning</t>
+          <t>Barrdominerat med lövinslag,  diameterspridning, död ved i olika nedbrytningsstadier  Koordinater fynd Geo tracker: 58°13′55.5″N, 15°29′00.3″E</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies subsp. abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1905,7 +1905,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123383615</v>
+        <v>123382241</v>
       </c>
       <c r="B11" t="n">
         <v>98396</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1948,11 +1948,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1961,13 +1957,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528366</v>
+        <v>528337</v>
       </c>
       <c r="R11" t="n">
-        <v>6454480</v>
+        <v>6454487</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1996,7 +1992,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2006,12 +2002,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2031,7 +2027,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2049,7 +2045,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123382746</v>
+        <v>123383615</v>
       </c>
       <c r="B12" t="n">
         <v>98396</v>
@@ -2084,7 +2080,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2092,7 +2088,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528338</v>
+        <v>528366</v>
       </c>
       <c r="R12" t="n">
-        <v>6454502</v>
+        <v>6454480</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>12 ex räknade.</t>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123382241</v>
+        <v>123382746</v>
       </c>
       <c r="B13" t="n">
         <v>98396</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2241,13 +2241,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528337</v>
+        <v>528338</v>
       </c>
       <c r="R13" t="n">
-        <v>6454487</v>
+        <v>6454502</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2773,6 +2773,153 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123784834</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5194</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-3, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>528354</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6454642</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrdominerat med visst inslag av löv.  Diameterspridning.</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Barrträd.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Barrträd.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -1905,7 +1905,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123382241</v>
+        <v>123383615</v>
       </c>
       <c r="B11" t="n">
         <v>98396</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1948,7 +1948,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1957,13 +1961,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528337</v>
+        <v>528366</v>
       </c>
       <c r="R11" t="n">
-        <v>6454487</v>
+        <v>6454480</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1992,7 +1996,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2002,12 +2006,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2027,7 +2031,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2045,7 +2049,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123383615</v>
+        <v>123382746</v>
       </c>
       <c r="B12" t="n">
         <v>98396</v>
@@ -2080,7 +2084,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2088,11 +2092,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528366</v>
+        <v>528338</v>
       </c>
       <c r="R12" t="n">
-        <v>6454480</v>
+        <v>6454502</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123382746</v>
+        <v>123382241</v>
       </c>
       <c r="B13" t="n">
         <v>98396</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2241,13 +2241,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528338</v>
+        <v>528337</v>
       </c>
       <c r="R13" t="n">
-        <v>6454502</v>
+        <v>6454487</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>12 ex räknade.</t>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,7 +1228,7 @@
         <v>122427546</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Min. 23 ex</t>
+          <t>37 räknade ex.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58o13 55.1 N, 15o28 59.7 E</t>
+          <t>Barrdominerat med inslag av löv. Gläntor. Lågor, stubbar, död ved i varierande nedbrytningsstadier förekommer.  OBS. Koordinater fyndplats via Geo tracker:  58°13′55.2″N, 15°28′59.9″E</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1905,7 +1905,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123383615</v>
+        <v>123382241</v>
       </c>
       <c r="B11" t="n">
         <v>98396</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1948,11 +1948,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1961,13 +1957,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528366</v>
+        <v>528337</v>
       </c>
       <c r="R11" t="n">
-        <v>6454480</v>
+        <v>6454487</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1996,7 +1992,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2006,12 +2002,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2031,7 +2027,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2049,7 +2045,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123382746</v>
+        <v>123383615</v>
       </c>
       <c r="B12" t="n">
         <v>98396</v>
@@ -2084,7 +2080,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2092,7 +2088,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528338</v>
+        <v>528366</v>
       </c>
       <c r="R12" t="n">
-        <v>6454502</v>
+        <v>6454480</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>12 ex räknade.</t>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123382241</v>
+        <v>123382746</v>
       </c>
       <c r="B13" t="n">
         <v>98396</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2241,13 +2241,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528337</v>
+        <v>528338</v>
       </c>
       <c r="R13" t="n">
-        <v>6454487</v>
+        <v>6454502</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2920,6 +2920,613 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123831648</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-7, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>528253</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6454527</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Mkt grov ved</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123832136</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-7, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>528253</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6454527</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Lövträd</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Lövträd</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123831433</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8436</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-7, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>528253</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6454527</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Betula</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123835185</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91398</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-7, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>528253</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6454527</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädrot</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>122428481</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>122427546</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>123035172</v>
       </c>
       <c r="B9" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>123383363</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123382241</v>
+        <v>123382746</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528337</v>
+        <v>528338</v>
       </c>
       <c r="R11" t="n">
-        <v>6454487</v>
+        <v>6454502</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123383615</v>
+        <v>123382241</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2088,11 +2088,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2101,13 +2097,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528366</v>
+        <v>528337</v>
       </c>
       <c r="R12" t="n">
-        <v>6454480</v>
+        <v>6454487</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2136,7 +2132,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2146,12 +2142,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2171,7 +2167,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2189,10 +2185,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123382746</v>
+        <v>123383615</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2224,7 +2220,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2232,7 +2228,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -2241,13 +2241,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528338</v>
+        <v>528366</v>
       </c>
       <c r="R13" t="n">
-        <v>6454502</v>
+        <v>6454480</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>12 ex räknade.</t>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
         <v>123380092</v>
       </c>
       <c r="B14" t="n">
-        <v>94885</v>
+        <v>94891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>123690103</v>
       </c>
       <c r="B15" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>123693724</v>
       </c>
       <c r="B16" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>123784834</v>
       </c>
       <c r="B17" t="n">
-        <v>5194</v>
+        <v>5196</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123831648</v>
+        <v>123835185</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>91398</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2934,37 +2934,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -3008,7 +3000,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3018,7 +3010,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3038,7 +3030,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
+          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3053,17 +3045,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Mkt grov ved</t>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädrot</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
+          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3081,10 +3073,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123832136</v>
+        <v>123831433</v>
       </c>
       <c r="B19" t="n">
-        <v>57506</v>
+        <v>8436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3093,33 +3085,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3164,7 +3157,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3174,7 +3167,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3183,6 +3181,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3191,19 +3190,29 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Lövträd</t>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Lövträd</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3221,10 +3230,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123831433</v>
+        <v>123833816</v>
       </c>
       <c r="B20" t="n">
-        <v>8436</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3233,36 +3242,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3305,7 +3316,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3315,12 +3326,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>*kläck/luft</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3340,27 +3346,32 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+          <t>Koordinater fynd Geo tracker: 58°13′52.8″N, 15°28′52.1″E</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3378,10 +3389,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123835185</v>
+        <v>123832136</v>
       </c>
       <c r="B21" t="n">
-        <v>91398</v>
+        <v>57506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3390,30 +3401,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3456,7 +3472,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3466,7 +3482,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3475,7 +3491,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3484,34 +3499,19 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Grov ved</t>
+          <t>Lövträd</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädrot</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Standing dead tree/snags # Lövträd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>122428481</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>122427546</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>123035172</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123383363</v>
+        <v>123380092</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>94893</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1777,37 +1777,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1817,13 +1809,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528362</v>
+        <v>528379</v>
       </c>
       <c r="R10" t="n">
-        <v>6454498</v>
+        <v>6454562</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1852,7 +1844,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1862,12 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>10 ex räknade.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1882,12 +1869,22 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1905,10 +1902,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123382746</v>
+        <v>123383615</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1940,7 +1937,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1948,7 +1945,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1957,13 +1958,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528338</v>
+        <v>528366</v>
       </c>
       <c r="R11" t="n">
-        <v>6454502</v>
+        <v>6454480</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1992,7 +1993,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2002,12 +2003,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>12 ex räknade.</t>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2022,12 +2023,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2048,7 +2049,7 @@
         <v>123382241</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2185,10 +2186,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123383615</v>
+        <v>123382746</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2220,7 +2221,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2228,11 +2229,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -2241,13 +2238,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528366</v>
+        <v>528338</v>
       </c>
       <c r="R13" t="n">
-        <v>6454480</v>
+        <v>6454502</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2276,7 +2273,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2286,12 +2283,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2306,12 +2303,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2329,10 +2326,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123380092</v>
+        <v>123383363</v>
       </c>
       <c r="B14" t="n">
-        <v>94891</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2341,29 +2338,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2373,13 +2378,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528379</v>
+        <v>528362</v>
       </c>
       <c r="R14" t="n">
-        <v>6454562</v>
+        <v>6454498</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2418,7 +2423,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 ex räknade.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2433,22 +2443,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123690103</v>
+        <v>123693724</v>
       </c>
       <c r="B15" t="n">
-        <v>57506</v>
+        <v>91010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2482,42 +2482,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-8, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528336</v>
+        <v>528354</v>
       </c>
       <c r="R15" t="n">
-        <v>6454669</v>
+        <v>6454642</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2549,7 +2552,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2559,7 +2562,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2568,6 +2571,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2578,27 +2582,32 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerat med lövinslag,  diameterspridning</t>
+          <t>Barrdominerat med lövinslag,  diameterspridning, död ved i olika nedbrytningsstadier  Koordinater fynd Geo tracker: 58°13′55.5″N, 15°29′00.3″E</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies subsp. abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2616,10 +2625,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123693724</v>
+        <v>123690103</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2632,45 +2641,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-8, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528354</v>
+        <v>528336</v>
       </c>
       <c r="R16" t="n">
-        <v>6454642</v>
+        <v>6454669</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2702,7 +2708,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2712,7 +2718,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2721,7 +2727,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2732,32 +2737,27 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrdominerat med lövinslag,  diameterspridning, död ved i olika nedbrytningsstadier  Koordinater fynd Geo tracker: 58°13′55.5″N, 15°29′00.3″E</t>
+          <t>Barrdominerat med lövinslag,  diameterspridning</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Grov ved</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Standing dead tree/snags # Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123835185</v>
+        <v>123831433</v>
       </c>
       <c r="B18" t="n">
-        <v>91398</v>
+        <v>8436</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2938,26 +2938,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5420</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3000,7 +3006,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3010,7 +3016,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3030,32 +3041,27 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Grov ved</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädrot</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3073,10 +3079,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123831433</v>
+        <v>123831648</v>
       </c>
       <c r="B19" t="n">
-        <v>8436</v>
+        <v>91010</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3085,36 +3091,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3157,7 +3165,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3167,12 +3175,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>*kläck/luft</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3192,27 +3195,32 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Mkt grov ved</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3230,10 +3238,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123833816</v>
+        <v>123835185</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>91400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3242,37 +3250,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Koordinater fynd Geo tracker: 58°13′52.8″N, 15°28′52.1″E</t>
+          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädrot</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3392,7 +3392,7 @@
         <v>123832136</v>
       </c>
       <c r="B21" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -1228,7 +1228,7 @@
         <v>122427546</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123380092</v>
+        <v>123383615</v>
       </c>
       <c r="B10" t="n">
-        <v>94893</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1777,30 +1777,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1809,10 +1821,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528379</v>
+        <v>528366</v>
       </c>
       <c r="R10" t="n">
-        <v>6454562</v>
+        <v>6454480</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1844,7 +1856,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1854,7 +1866,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1869,22 +1886,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1902,10 +1909,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123383615</v>
+        <v>123382746</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1937,7 +1944,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1945,11 +1952,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1958,13 +1961,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528366</v>
+        <v>528338</v>
       </c>
       <c r="R11" t="n">
-        <v>6454480</v>
+        <v>6454502</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1993,7 +1996,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2003,12 +2006,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2023,12 +2026,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2049,7 +2052,7 @@
         <v>123382241</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2186,10 +2189,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123382746</v>
+        <v>123380092</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>95401</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2198,37 +2201,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -2238,13 +2233,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528338</v>
+        <v>528379</v>
       </c>
       <c r="R13" t="n">
-        <v>6454502</v>
+        <v>6454562</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2273,7 +2268,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2283,12 +2278,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>12 ex räknade.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2303,12 +2293,22 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2329,7 +2329,7 @@
         <v>123383363</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123693724</v>
+        <v>123690103</v>
       </c>
       <c r="B15" t="n">
-        <v>91010</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2482,45 +2482,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-8, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528354</v>
+        <v>528336</v>
       </c>
       <c r="R15" t="n">
-        <v>6454642</v>
+        <v>6454669</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2552,7 +2549,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2562,7 +2559,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2571,7 +2568,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2582,32 +2578,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerat med lövinslag,  diameterspridning, död ved i olika nedbrytningsstadier  Koordinater fynd Geo tracker: 58°13′55.5″N, 15°29′00.3″E</t>
+          <t>Barrdominerat med lövinslag,  diameterspridning</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Grov ved</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Standing dead tree/snags # Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2625,10 +2616,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123690103</v>
+        <v>123693724</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>91010</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2641,42 +2632,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-8, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528336</v>
+        <v>528354</v>
       </c>
       <c r="R16" t="n">
-        <v>6454669</v>
+        <v>6454642</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2708,7 +2702,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2718,7 +2712,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2727,6 +2721,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2737,27 +2732,32 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrdominerat med lövinslag,  diameterspridning</t>
+          <t>Barrdominerat med lövinslag,  diameterspridning, död ved i olika nedbrytningsstadier  Koordinater fynd Geo tracker: 58°13′55.5″N, 15°29′00.3″E</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies subsp. abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123831433</v>
+        <v>123835547</v>
       </c>
       <c r="B18" t="n">
-        <v>8436</v>
+        <v>91010</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2934,36 +2934,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3006,7 +3008,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3016,12 +3018,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>*kläck/luft</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3041,27 +3038,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+          <t>Rikligt med död ved si olika nedbrytningsstadier. Diameterspridning.  Fyndplats Geo tracker: 58°13′53.3″N, 15°28′52.7″E</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3079,10 +3081,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123831648</v>
+        <v>123832136</v>
       </c>
       <c r="B19" t="n">
-        <v>91010</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3095,34 +3097,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3165,7 +3164,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3175,7 +3174,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3184,7 +3183,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3193,34 +3191,19 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Mkt grov ved</t>
+          <t>Lövträd</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
+          <t>Standing dead tree/snags # Lövträd</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3238,10 +3221,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123835185</v>
+        <v>123831433</v>
       </c>
       <c r="B20" t="n">
-        <v>91400</v>
+        <v>8436</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3254,26 +3237,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3316,7 +3305,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3326,7 +3315,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3346,32 +3340,27 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Grov ved</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädrot</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3389,10 +3378,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123832136</v>
+        <v>123835185</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>91400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3401,35 +3390,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3472,7 +3456,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3482,7 +3466,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3491,6 +3475,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3499,19 +3484,34 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Lövträd</t>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädrot</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Lövträd</t>
+          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -1909,7 +1909,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123382746</v>
+        <v>123382241</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1961,13 +1961,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528338</v>
+        <v>528337</v>
       </c>
       <c r="R11" t="n">
-        <v>6454502</v>
+        <v>6454487</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>12 ex räknade.</t>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2049,7 +2049,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123382241</v>
+        <v>123383363</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528337</v>
+        <v>528362</v>
       </c>
       <c r="R12" t="n">
-        <v>6454487</v>
+        <v>6454498</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+          <t>10 ex räknade.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123380092</v>
+        <v>123382746</v>
       </c>
       <c r="B13" t="n">
-        <v>95401</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2201,29 +2201,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -2233,13 +2241,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528379</v>
+        <v>528338</v>
       </c>
       <c r="R13" t="n">
-        <v>6454562</v>
+        <v>6454502</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2268,7 +2276,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2278,7 +2286,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2293,22 +2306,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2326,10 +2329,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123383363</v>
+        <v>123380092</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>95401</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2338,37 +2341,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2378,13 +2373,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528362</v>
+        <v>528379</v>
       </c>
       <c r="R14" t="n">
-        <v>6454498</v>
+        <v>6454562</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2423,12 +2418,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 ex räknade.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2443,12 +2433,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123835547</v>
+        <v>123831433</v>
       </c>
       <c r="B18" t="n">
-        <v>91010</v>
+        <v>8436</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2934,38 +2934,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3008,7 +3006,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3018,7 +3016,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3038,32 +3041,27 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Rikligt med död ved si olika nedbrytningsstadier. Diameterspridning.  Fyndplats Geo tracker: 58°13′53.3″N, 15°28′52.7″E</t>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Grov ved</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3221,10 +3219,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123831433</v>
+        <v>123835547</v>
       </c>
       <c r="B20" t="n">
-        <v>8436</v>
+        <v>91010</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3233,36 +3231,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3315,12 +3315,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>*kläck/luft</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3340,27 +3335,32 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+          <t>Rikligt med död ved si olika nedbrytningsstadier. Diameterspridning.  Fyndplats Geo tracker: 58°13′53.3″N, 15°28′52.7″E</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -2049,10 +2049,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123383363</v>
+        <v>123380092</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>95401</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2061,37 +2061,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -2101,13 +2093,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528362</v>
+        <v>528379</v>
       </c>
       <c r="R12" t="n">
-        <v>6454498</v>
+        <v>6454562</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2136,7 +2128,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2146,12 +2138,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>10 ex räknade.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,12 +2153,22 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2189,7 +2186,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123382746</v>
+        <v>123383363</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -2224,7 +2221,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2241,13 +2238,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528338</v>
+        <v>528362</v>
       </c>
       <c r="R13" t="n">
-        <v>6454502</v>
+        <v>6454498</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2276,7 +2273,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2286,12 +2283,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>12 ex räknade.</t>
+          <t>10 ex räknade.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2311,7 +2308,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2329,10 +2326,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123380092</v>
+        <v>123382746</v>
       </c>
       <c r="B14" t="n">
-        <v>95401</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2341,29 +2338,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2373,13 +2378,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528379</v>
+        <v>528338</v>
       </c>
       <c r="R14" t="n">
-        <v>6454562</v>
+        <v>6454502</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2418,7 +2423,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2433,22 +2443,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123831433</v>
+        <v>123833816</v>
       </c>
       <c r="B18" t="n">
-        <v>8436</v>
+        <v>91010</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2934,36 +2934,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3006,7 +3008,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3016,12 +3018,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>*kläck/luft</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3041,27 +3038,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+          <t>Koordinater fynd Geo tracker: 58°13′52.8″N, 15°28′52.1″E</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3079,10 +3081,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123832136</v>
+        <v>123835185</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>91400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3091,35 +3093,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3162,7 +3159,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3172,7 +3169,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3181,6 +3178,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3189,19 +3187,34 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Lövträd</t>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädrot</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Lövträd</t>
+          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3219,10 +3232,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123835547</v>
+        <v>123831433</v>
       </c>
       <c r="B20" t="n">
-        <v>91010</v>
+        <v>8436</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3231,38 +3244,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3305,7 +3316,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3315,7 +3326,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3335,32 +3351,27 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Rikligt med död ved si olika nedbrytningsstadier. Diameterspridning.  Fyndplats Geo tracker: 58°13′53.3″N, 15°28′52.7″E</t>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Grov ved</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3378,10 +3389,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123835185</v>
+        <v>123832136</v>
       </c>
       <c r="B21" t="n">
-        <v>91400</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3390,30 +3401,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3456,7 +3472,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3466,7 +3482,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3475,7 +3491,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3484,34 +3499,19 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Grov ved</t>
+          <t>Lövträd</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädrot</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Standing dead tree/snags # Lövträd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -1765,7 +1765,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123383615</v>
+        <v>123382746</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1808,11 +1808,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1821,13 +1817,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528366</v>
+        <v>528338</v>
       </c>
       <c r="R10" t="n">
-        <v>6454480</v>
+        <v>6454502</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1866,12 +1862,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1886,12 +1882,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1909,7 +1905,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123382241</v>
+        <v>123383615</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1944,7 +1940,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>136</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1952,7 +1948,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1961,13 +1961,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528337</v>
+        <v>528366</v>
       </c>
       <c r="R11" t="n">
-        <v>6454487</v>
+        <v>6454480</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123380092</v>
+        <v>123382241</v>
       </c>
       <c r="B12" t="n">
-        <v>95401</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2061,29 +2061,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -2093,13 +2101,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528379</v>
+        <v>528337</v>
       </c>
       <c r="R12" t="n">
-        <v>6454562</v>
+        <v>6454487</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2128,7 +2136,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2138,7 +2146,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2153,22 +2166,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2326,10 +2329,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123382746</v>
+        <v>123380092</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>95401</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2338,37 +2341,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2378,13 +2373,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528338</v>
+        <v>528379</v>
       </c>
       <c r="R14" t="n">
-        <v>6454502</v>
+        <v>6454562</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2423,12 +2418,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>12 ex räknade.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2443,12 +2433,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123833816</v>
+        <v>123831648</v>
       </c>
       <c r="B18" t="n">
         <v>91010</v>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Koordinater fynd Geo tracker: 58°13′52.8″N, 15°28′52.1″E</t>
+          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Grov ved</t>
+          <t>Mkt grov ved</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123835185</v>
+        <v>123831433</v>
       </c>
       <c r="B19" t="n">
-        <v>91400</v>
+        <v>8436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3097,26 +3097,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5420</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3159,7 +3165,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3169,7 +3175,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3189,32 +3200,27 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Grov ved</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädrot</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3232,10 +3238,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123831433</v>
+        <v>123832136</v>
       </c>
       <c r="B20" t="n">
-        <v>8436</v>
+        <v>57507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3244,34 +3250,33 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3316,7 +3321,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3326,12 +3331,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>*kläck/luft</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3340,7 +3340,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3349,29 +3348,19 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Betula</t>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Lövträd</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Standing dead tree/snags # Lövträd</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3389,10 +3378,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123832136</v>
+        <v>123835185</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>91400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3401,35 +3390,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3472,7 +3456,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3482,7 +3466,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3491,6 +3475,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3499,19 +3484,34 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Lövträd</t>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädrot</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Lövträd</t>
+          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -1765,10 +1765,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123382746</v>
+        <v>123380092</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>95401</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1777,37 +1777,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1817,13 +1809,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528338</v>
+        <v>528379</v>
       </c>
       <c r="R10" t="n">
-        <v>6454502</v>
+        <v>6454562</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1852,7 +1844,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1862,12 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>12 ex räknade.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1882,12 +1869,22 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
+          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1905,7 +1902,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123383615</v>
+        <v>123383363</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1940,7 +1937,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1948,11 +1945,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1961,13 +1954,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528366</v>
+        <v>528362</v>
       </c>
       <c r="R11" t="n">
-        <v>6454480</v>
+        <v>6454498</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1996,7 +1989,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2006,12 +1999,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>136 ex räknade, sannolikt fler.</t>
+          <t>10 ex räknade.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2026,12 +2019,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
+          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2049,7 +2042,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123382241</v>
+        <v>123382746</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -2084,7 +2077,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2101,13 +2094,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528337</v>
+        <v>528338</v>
       </c>
       <c r="R12" t="n">
-        <v>6454487</v>
+        <v>6454502</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2136,7 +2129,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2146,12 +2139,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
+          <t>12 ex räknade.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,12 +2159,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
+          <t>Barrskog med gran och tall, inslag av löv så som björk och asp.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2189,7 +2182,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123383363</v>
+        <v>123382241</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -2224,7 +2217,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2241,10 +2234,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528362</v>
+        <v>528337</v>
       </c>
       <c r="R13" t="n">
-        <v>6454498</v>
+        <v>6454487</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2276,7 +2269,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2286,12 +2279,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>10 ex räknade.</t>
+          <t>61 ex räknade, varav 4 med fjolårsstängel. Från slutet av skogsgrusvägen, rakt fram-svagt åt höger (sydlig riktning), ca 20-30 meter in.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2306,12 +2299,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrskog, grandominerat, men även riktigt med tall. Inslag av löv så som björk och asp.</t>
+          <t>Barrnaturskog som domineras av gran, men innehåller även tall. Inlag av lövträd så som björk och asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2329,10 +2322,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123380092</v>
+        <v>123383615</v>
       </c>
       <c r="B14" t="n">
-        <v>95401</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2341,30 +2334,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2373,10 +2378,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528379</v>
+        <v>528366</v>
       </c>
       <c r="R14" t="n">
-        <v>6454562</v>
+        <v>6454480</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2418,7 +2423,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>136 ex räknade, sannolikt fler.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2433,22 +2443,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Beskuggad bergsbrant, dominerat av gran, men även riktigt med tall och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+          <t>Flerskiktad grandominerad barrnaturskog. Även ganska mycket tall och inslag av löv, så som björk och asp.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123690103</v>
+        <v>123693724</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>91010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2482,42 +2482,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-8, Ög</t>
+          <t>Vallsnäs skog 1-3, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528336</v>
+        <v>528354</v>
       </c>
       <c r="R15" t="n">
-        <v>6454669</v>
+        <v>6454642</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2549,7 +2552,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2559,7 +2562,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2568,6 +2571,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2578,27 +2582,32 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerat med lövinslag,  diameterspridning</t>
+          <t>Barrdominerat med lövinslag,  diameterspridning, död ved i olika nedbrytningsstadier  Koordinater fynd Geo tracker: 58°13′55.5″N, 15°29′00.3″E</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies subsp. abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2616,10 +2625,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123693724</v>
+        <v>123690103</v>
       </c>
       <c r="B16" t="n">
-        <v>91010</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2632,45 +2641,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-3, Ög</t>
+          <t>Vallsnäs skog 1-8, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528354</v>
+        <v>528336</v>
       </c>
       <c r="R16" t="n">
-        <v>6454642</v>
+        <v>6454669</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2702,7 +2708,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2712,7 +2718,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2721,7 +2727,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2732,32 +2737,27 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrdominerat med lövinslag,  diameterspridning, död ved i olika nedbrytningsstadier  Koordinater fynd Geo tracker: 58°13′55.5″N, 15°29′00.3″E</t>
+          <t>Barrdominerat med lövinslag,  diameterspridning</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Grov ved</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Standing dead tree/snags # Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123831648</v>
+        <v>123831433</v>
       </c>
       <c r="B18" t="n">
-        <v>91010</v>
+        <v>8436</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2934,38 +2934,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3008,7 +3006,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3018,7 +3016,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3038,32 +3041,27 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Mkt grov ved</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3081,10 +3079,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123831433</v>
+        <v>123833816</v>
       </c>
       <c r="B19" t="n">
-        <v>8436</v>
+        <v>91010</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3093,36 +3091,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3175,12 +3175,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>*kläck/luft</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3200,27 +3195,32 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+          <t>Koordinater fynd Geo tracker: 58°13′52.8″N, 15°28′52.1″E</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -2922,10 +2922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123831648</v>
+        <v>123835185</v>
       </c>
       <c r="B18" t="n">
-        <v>91032</v>
+        <v>91422</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2934,37 +2934,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -3008,7 +3000,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3018,7 +3010,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3038,7 +3030,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
+          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3053,17 +3045,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Mkt grov ved</t>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädrot</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
+          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3081,10 +3073,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123831433</v>
+        <v>123831648</v>
       </c>
       <c r="B19" t="n">
-        <v>8436</v>
+        <v>91032</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3093,36 +3085,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3165,7 +3159,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3175,12 +3169,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>*kläck/luft</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3200,27 +3189,32 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Mkt grov ved</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3238,10 +3232,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123832136</v>
+        <v>123831433</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>8436</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3250,33 +3244,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3321,7 +3316,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3331,7 +3326,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3340,6 +3340,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3348,19 +3349,29 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Lövträd</t>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Lövträd</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3378,10 +3389,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123835185</v>
+        <v>123832136</v>
       </c>
       <c r="B21" t="n">
-        <v>91422</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3390,30 +3401,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3456,7 +3472,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3466,7 +3482,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3475,7 +3491,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3484,34 +3499,19 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Grov ved</t>
+          <t>Lövträd</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädrot</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Standing dead tree/snags # Lövträd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -2922,10 +2922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123835185</v>
+        <v>123832136</v>
       </c>
       <c r="B18" t="n">
-        <v>91422</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2934,30 +2934,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3000,7 +3005,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3010,7 +3015,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3019,7 +3024,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3028,34 +3032,19 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Grov ved</t>
+          <t>Lövträd</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädrot</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
+          <t>Standing dead tree/snags # Lövträd</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3073,10 +3062,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123831648</v>
+        <v>123831433</v>
       </c>
       <c r="B19" t="n">
-        <v>91032</v>
+        <v>8436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3085,38 +3074,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3159,7 +3146,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3169,7 +3156,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3189,32 +3181,27 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Mkt grov ved</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3232,10 +3219,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123831433</v>
+        <v>123831648</v>
       </c>
       <c r="B20" t="n">
-        <v>8436</v>
+        <v>91032</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3244,36 +3231,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3316,7 +3305,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3326,12 +3315,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>*kläck/luft</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3351,27 +3335,32 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Mkt grov ved</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3389,10 +3378,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123832136</v>
+        <v>123835185</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>91422</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3401,35 +3390,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3472,7 +3456,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3482,7 +3466,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3491,6 +3475,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3499,19 +3484,34 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Rikligt med död ved i olika  nedbrytningsstadier, diameterspridning.  Fyndplats Geo tracker: 58°13′51.4″N, 15°28′52.5″E</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Lövträd</t>
+          <t>Grov ved</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädrot</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Lövträd</t>
+          <t>Tree root # Pinus sylvestris var. sylvestris # Grov ved</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3062,10 +3062,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123831433</v>
+        <v>123831648</v>
       </c>
       <c r="B19" t="n">
-        <v>8436</v>
+        <v>91032</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3074,36 +3074,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3146,7 +3148,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3156,12 +3158,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>*kläck/luft</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3181,27 +3178,32 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
+          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vanlig tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Mkt grov ved</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3219,10 +3221,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123831648</v>
+        <v>123831433</v>
       </c>
       <c r="B20" t="n">
-        <v>91032</v>
+        <v>8436</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3231,38 +3233,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3315,7 +3315,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3335,32 +3340,27 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Fynd geo tracker: 58°13′52.4″N, 15°28′50.1″E</t>
+          <t>Fynd geo tracker: 58°13′52.6″N, 15°28′50.6″E</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>vanlig tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Mkt grov ved</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris var. sylvestris # Mkt grov ved</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,6 +3527,266 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125334687</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-1, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>528360</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6454489</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125335405</v>
+      </c>
+      <c r="B23" t="n">
+        <v>105029</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-9, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>528205</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6454473</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Glänta</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3529,10 +3529,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125334687</v>
+        <v>125335405</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>105029</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3541,49 +3541,53 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-9, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528360</v>
+        <v>528205</v>
       </c>
       <c r="R22" t="n">
-        <v>6454489</v>
+        <v>6454473</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3612,7 +3616,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3622,7 +3626,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3631,12 +3635,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Glänta</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3654,10 +3664,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125335405</v>
+        <v>125334687</v>
       </c>
       <c r="B23" t="n">
-        <v>105029</v>
+        <v>57666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3666,53 +3676,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221141</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-9, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528205</v>
+        <v>528360</v>
       </c>
       <c r="R23" t="n">
-        <v>6454473</v>
+        <v>6454489</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3741,7 +3747,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3751,7 +3757,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3760,18 +3766,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Glänta</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3529,10 +3529,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125335405</v>
+        <v>125334687</v>
       </c>
       <c r="B22" t="n">
-        <v>105029</v>
+        <v>57793</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3541,53 +3541,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-9, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528205</v>
+        <v>528360</v>
       </c>
       <c r="R22" t="n">
-        <v>6454473</v>
+        <v>6454489</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3616,7 +3612,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3626,7 +3622,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3635,18 +3631,12 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Glänta</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3664,10 +3654,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125334687</v>
+        <v>125335405</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>105205</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3676,49 +3666,53 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>221141</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-9, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528360</v>
+        <v>528205</v>
       </c>
       <c r="R23" t="n">
-        <v>6454489</v>
+        <v>6454473</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3747,7 +3741,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3757,7 +3751,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3766,12 +3760,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Glänta</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3529,10 +3529,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125334687</v>
+        <v>125335405</v>
       </c>
       <c r="B22" t="n">
-        <v>57793</v>
+        <v>105205</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3541,49 +3541,53 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-1, Ög</t>
+          <t>Vallsnäs skog 1-9, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528360</v>
+        <v>528205</v>
       </c>
       <c r="R22" t="n">
-        <v>6454489</v>
+        <v>6454473</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3612,7 +3616,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3622,7 +3626,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3631,12 +3635,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Glänta</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3654,10 +3664,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125335405</v>
+        <v>125334687</v>
       </c>
       <c r="B23" t="n">
-        <v>105205</v>
+        <v>57793</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3666,53 +3676,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221141</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 1-9, Ög</t>
+          <t>Vallsnäs skog 1-1, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528205</v>
+        <v>528360</v>
       </c>
       <c r="R23" t="n">
-        <v>6454473</v>
+        <v>6454489</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3741,7 +3747,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3751,7 +3757,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3760,18 +3766,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Glänta</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3532,12 +3532,7 @@
         <v>125335405</v>
       </c>
       <c r="B22" t="n">
-        <v>105205</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3667,12 +3662,7 @@
         <v>125334687</v>
       </c>
       <c r="B23" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3532,7 +3532,7 @@
         <v>125335405</v>
       </c>
       <c r="B22" t="n">
-        <v>105260</v>
+        <v>105267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3532,7 +3532,7 @@
         <v>125335405</v>
       </c>
       <c r="B22" t="n">
-        <v>105267</v>
+        <v>105270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3532,7 +3532,7 @@
         <v>125335405</v>
       </c>
       <c r="B22" t="n">
-        <v>105270</v>
+        <v>105274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3777,6 +3777,271 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128408952</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-3, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>528354</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6454642</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrdominerat m lövinslag</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128408697</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92055</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-3, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>528354</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6454642</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Barrdominerat  58°13′55.3″N, 15°28′58.2″E Koordinater Geotracker:</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3907,7 +3907,7 @@
         <v>128408697</v>
       </c>
       <c r="B25" t="n">
-        <v>92055</v>
+        <v>92057</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3782,7 +3782,7 @@
         <v>128408952</v>
       </c>
       <c r="B24" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128408697</v>
       </c>
       <c r="B25" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3782,7 +3782,7 @@
         <v>128408952</v>
       </c>
       <c r="B24" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128408697</v>
       </c>
       <c r="B25" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3907,7 +3907,7 @@
         <v>128408697</v>
       </c>
       <c r="B25" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3907,7 +3907,7 @@
         <v>128408697</v>
       </c>
       <c r="B25" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3782,7 +3782,7 @@
         <v>128408952</v>
       </c>
       <c r="B24" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128408697</v>
       </c>
       <c r="B25" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3907,7 +3907,7 @@
         <v>128408697</v>
       </c>
       <c r="B25" t="n">
-        <v>92191</v>
+        <v>92201</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3782,7 +3782,7 @@
         <v>128408952</v>
       </c>
       <c r="B24" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128408697</v>
       </c>
       <c r="B25" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -3782,7 +3782,7 @@
         <v>128408952</v>
       </c>
       <c r="B24" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128408697</v>
       </c>
       <c r="B25" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4042,6 +4042,241 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129876169</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>528346</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6454655</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>E-Lin-0980</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sammanslagning av 8 rapporter</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129876251</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 1-7, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>528253</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6454527</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>E-Lin-1012</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -4047,7 +4047,7 @@
         <v>129876169</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129876251</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -4047,7 +4047,7 @@
         <v>129876169</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129876251</v>
       </c>
       <c r="B27" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -4047,7 +4047,7 @@
         <v>129876169</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129876251</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -4047,7 +4047,7 @@
         <v>129876169</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129876251</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -4047,7 +4047,7 @@
         <v>129876169</v>
       </c>
       <c r="B26" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129876251</v>
       </c>
       <c r="B27" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -4047,7 +4047,7 @@
         <v>129876169</v>
       </c>
       <c r="B26" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129876251</v>
       </c>
       <c r="B27" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 8914-2024 artfynd.xlsx
+++ b/artfynd/A 8914-2024 artfynd.xlsx
@@ -4047,7 +4047,7 @@
         <v>129876169</v>
       </c>
       <c r="B26" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129876251</v>
       </c>
       <c r="B27" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
